--- a/04_Output/2026_PFOS_SS_Final_FCAs.xlsx
+++ b/04_Output/2026_PFOS_SS_Final_FCAs.xlsx
@@ -502,6 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -597,7 +598,7 @@
       <c r="Y1" s="11"/>
       <c r="Z1" s="11"/>
     </row>
-    <row r="2" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -660,7 +661,7 @@
       <c r="Z2" s="6"/>
       <c r="AA2" s="7"/>
     </row>
-    <row r="3" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -723,7 +724,7 @@
       <c r="Z3" s="6"/>
       <c r="AA3" s="7"/>
     </row>
-    <row r="4" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>39</v>
       </c>
@@ -786,7 +787,7 @@
       <c r="Z4" s="6"/>
       <c r="AA4" s="7"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>39</v>
       </c>
@@ -848,7 +849,7 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -910,7 +911,7 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -974,7 +975,7 @@
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
     </row>
-    <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1166,7 +1167,7 @@
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
@@ -1430,7 +1431,7 @@
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -1494,7 +1495,7 @@
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
@@ -1556,7 +1557,7 @@
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -2851,6 +2852,11 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:Z21">
+    <filterColumn colId="18">
+      <filters>
+        <filter val="Take to TAC"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:Z21">
       <sortCondition ref="P1:P21"/>
     </sortState>
